--- a/SWP391_SE20A09_DE190022.xlsx
+++ b/SWP391_SE20A09_DE190022.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SWP_AUDITLOG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\swp391-aiauditlog-HuyHoang1233\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9192" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9192" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -2100,7 +2100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2144,9 +2144,6 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2159,27 +2156,8 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2211,9 +2189,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
@@ -2224,6 +2199,25 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2539,14 +2533,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
     </row>
     <row r="3" spans="1:6" ht="18">
       <c r="A3" s="1" t="s">
@@ -2690,7 +2684,7 @@
       <c r="A20" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="B20" s="27" t="s">
+      <c r="B20" s="26" t="s">
         <v>163</v>
       </c>
       <c r="C20" s="20" t="s">
@@ -2784,28 +2778,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
     </row>
     <row r="2" spans="1:11" ht="30" customHeight="1">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="44" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
     </row>
     <row r="3" spans="1:11" ht="40.049999999999997" customHeight="1">
       <c r="A3" s="6" t="s">
@@ -2843,19 +2837,19 @@
       <c r="C4" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="46" t="s">
+      <c r="D4" s="48" t="s">
         <v>119</v>
       </c>
-      <c r="E4" s="28" t="s">
+      <c r="E4" s="37" t="s">
         <v>120</v>
       </c>
-      <c r="F4" s="28" t="s">
+      <c r="F4" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="G4" s="45" t="s">
+      <c r="G4" s="37" t="s">
         <v>122</v>
       </c>
-      <c r="H4" s="45" t="s">
+      <c r="H4" s="37" t="s">
         <v>123</v>
       </c>
       <c r="I4" s="20"/>
@@ -2872,19 +2866,19 @@
       <c r="C5" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="28" t="s">
+      <c r="D5" s="37" t="s">
         <v>124</v>
       </c>
       <c r="E5" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="F5" s="28" t="s">
+      <c r="F5" s="37" t="s">
         <v>126</v>
       </c>
-      <c r="G5" s="23" t="s">
+      <c r="G5" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="H5" s="28" t="s">
+      <c r="H5" s="37" t="s">
         <v>128</v>
       </c>
       <c r="I5" s="21"/>
@@ -2910,7 +2904,7 @@
       <c r="F6" s="22" t="s">
         <v>131</v>
       </c>
-      <c r="G6" s="23" t="s">
+      <c r="G6" s="22" t="s">
         <v>132</v>
       </c>
       <c r="H6" s="22" t="s">
@@ -2939,7 +2933,7 @@
       <c r="F7" s="22" t="s">
         <v>136</v>
       </c>
-      <c r="G7" s="23" t="s">
+      <c r="G7" s="22" t="s">
         <v>137</v>
       </c>
       <c r="H7" s="22" t="s">
@@ -2968,7 +2962,7 @@
       <c r="F8" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="G8" s="23" t="s">
+      <c r="G8" s="22" t="s">
         <v>142</v>
       </c>
       <c r="H8" s="22" t="s">
@@ -2994,16 +2988,16 @@
       <c r="E9" s="22" t="s">
         <v>145</v>
       </c>
-      <c r="F9" s="28" t="s">
+      <c r="F9" s="37" t="s">
         <v>146</v>
       </c>
-      <c r="G9" s="23" t="s">
+      <c r="G9" s="22" t="s">
         <v>147</v>
       </c>
       <c r="H9" s="22" t="s">
         <v>148</v>
       </c>
-      <c r="I9" s="23"/>
+      <c r="I9" s="22"/>
       <c r="J9" s="20"/>
       <c r="K9" s="21"/>
     </row>
@@ -3026,13 +3020,13 @@
       <c r="F10" s="22" t="s">
         <v>151</v>
       </c>
-      <c r="G10" s="23" t="s">
+      <c r="G10" s="22" t="s">
         <v>152</v>
       </c>
       <c r="H10" s="22" t="s">
         <v>153</v>
       </c>
-      <c r="I10" s="24"/>
+      <c r="I10" s="23"/>
       <c r="J10" s="21"/>
       <c r="K10" s="21"/>
     </row>
@@ -3067,450 +3061,450 @@
       <c r="H13" s="7"/>
     </row>
     <row r="14" spans="1:11" ht="79.95" customHeight="1">
-      <c r="A14" s="37" t="s">
+      <c r="A14" s="29" t="s">
         <v>262</v>
       </c>
-      <c r="B14" s="37"/>
-      <c r="C14" s="37"/>
-      <c r="D14" s="37"/>
-      <c r="E14" s="37"/>
-      <c r="F14" s="37"/>
+      <c r="B14" s="29"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="29"/>
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
     </row>
     <row r="15" spans="1:11" ht="79.95" customHeight="1">
-      <c r="A15" s="44" t="s">
+      <c r="A15" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="B15" s="44" t="s">
+      <c r="B15" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="C15" s="44" t="s">
+      <c r="C15" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="44" t="s">
+      <c r="D15" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="44" t="s">
+      <c r="E15" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="F15" s="44" t="s">
+      <c r="F15" s="36" t="s">
         <v>39</v>
       </c>
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
     </row>
     <row r="16" spans="1:11" ht="79.95" customHeight="1">
-      <c r="A16" s="37" t="s">
+      <c r="A16" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="37" t="s">
+      <c r="B16" s="29" t="s">
         <v>176</v>
       </c>
-      <c r="C16" s="37" t="s">
+      <c r="C16" s="29" t="s">
         <v>177</v>
       </c>
-      <c r="D16" s="37" t="s">
+      <c r="D16" s="29" t="s">
         <v>178</v>
       </c>
-      <c r="E16" s="37" t="s">
+      <c r="E16" s="29" t="s">
         <v>263</v>
       </c>
-      <c r="F16" s="37" t="s">
+      <c r="F16" s="29" t="s">
         <v>179</v>
       </c>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
     </row>
     <row r="17" spans="1:8" ht="79.95" customHeight="1">
-      <c r="A17" s="37" t="s">
+      <c r="A17" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="37" t="s">
+      <c r="B17" s="29" t="s">
         <v>180</v>
       </c>
-      <c r="C17" s="37" t="s">
+      <c r="C17" s="29" t="s">
         <v>181</v>
       </c>
-      <c r="D17" s="37" t="s">
+      <c r="D17" s="29" t="s">
         <v>182</v>
       </c>
-      <c r="E17" s="37" t="s">
+      <c r="E17" s="29" t="s">
         <v>264</v>
       </c>
-      <c r="F17" s="37" t="s">
+      <c r="F17" s="29" t="s">
         <v>183</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
     </row>
     <row r="18" spans="1:8" ht="79.95" customHeight="1">
-      <c r="A18" s="37" t="s">
+      <c r="A18" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="37" t="s">
+      <c r="B18" s="29" t="s">
         <v>184</v>
       </c>
-      <c r="C18" s="37" t="s">
+      <c r="C18" s="29" t="s">
         <v>185</v>
       </c>
-      <c r="D18" s="37" t="s">
+      <c r="D18" s="29" t="s">
         <v>186</v>
       </c>
-      <c r="E18" s="37" t="s">
+      <c r="E18" s="29" t="s">
         <v>187</v>
       </c>
-      <c r="F18" s="37" t="s">
+      <c r="F18" s="29" t="s">
         <v>188</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7"/>
     </row>
     <row r="19" spans="1:8" ht="79.95" customHeight="1">
-      <c r="A19" s="37" t="s">
+      <c r="A19" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="37" t="s">
+      <c r="B19" s="29" t="s">
         <v>189</v>
       </c>
-      <c r="C19" s="37" t="s">
+      <c r="C19" s="29" t="s">
         <v>190</v>
       </c>
-      <c r="D19" s="37" t="s">
+      <c r="D19" s="29" t="s">
         <v>191</v>
       </c>
-      <c r="E19" s="37" t="s">
+      <c r="E19" s="29" t="s">
         <v>265</v>
       </c>
-      <c r="F19" s="37" t="s">
+      <c r="F19" s="29" t="s">
         <v>192</v>
       </c>
       <c r="G19" s="7"/>
       <c r="H19" s="7"/>
     </row>
     <row r="20" spans="1:8" ht="79.95" customHeight="1">
-      <c r="A20" s="37" t="s">
+      <c r="A20" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="37" t="s">
+      <c r="B20" s="29" t="s">
         <v>193</v>
       </c>
-      <c r="C20" s="37" t="s">
+      <c r="C20" s="29" t="s">
         <v>194</v>
       </c>
-      <c r="D20" s="37" t="s">
+      <c r="D20" s="29" t="s">
         <v>195</v>
       </c>
-      <c r="E20" s="37" t="s">
+      <c r="E20" s="29" t="s">
         <v>266</v>
       </c>
-      <c r="F20" s="37" t="s">
+      <c r="F20" s="29" t="s">
         <v>196</v>
       </c>
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
     </row>
     <row r="21" spans="1:8" ht="79.95" customHeight="1">
-      <c r="A21" s="37" t="s">
+      <c r="A21" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="37" t="s">
+      <c r="B21" s="29" t="s">
         <v>197</v>
       </c>
-      <c r="C21" s="37" t="s">
+      <c r="C21" s="29" t="s">
         <v>198</v>
       </c>
-      <c r="D21" s="37" t="s">
+      <c r="D21" s="29" t="s">
         <v>199</v>
       </c>
-      <c r="E21" s="37" t="s">
+      <c r="E21" s="29" t="s">
         <v>267</v>
       </c>
-      <c r="F21" s="37" t="s">
+      <c r="F21" s="29" t="s">
         <v>200</v>
       </c>
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
     </row>
     <row r="22" spans="1:8" ht="79.95" customHeight="1">
-      <c r="A22" s="37" t="s">
+      <c r="A22" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="B22" s="37" t="s">
+      <c r="B22" s="29" t="s">
         <v>201</v>
       </c>
-      <c r="C22" s="37" t="s">
+      <c r="C22" s="29" t="s">
         <v>202</v>
       </c>
-      <c r="D22" s="37" t="s">
+      <c r="D22" s="29" t="s">
         <v>203</v>
       </c>
-      <c r="E22" s="37" t="s">
+      <c r="E22" s="29" t="s">
         <v>268</v>
       </c>
-      <c r="F22" s="37" t="s">
+      <c r="F22" s="29" t="s">
         <v>204</v>
       </c>
       <c r="G22" s="7"/>
       <c r="H22" s="7"/>
     </row>
     <row r="23" spans="1:8" ht="79.95" customHeight="1">
-      <c r="A23" s="37" t="s">
+      <c r="A23" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="37" t="s">
+      <c r="B23" s="29" t="s">
         <v>205</v>
       </c>
-      <c r="C23" s="37" t="s">
+      <c r="C23" s="29" t="s">
         <v>206</v>
       </c>
-      <c r="D23" s="37" t="s">
+      <c r="D23" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="E23" s="37" t="s">
+      <c r="E23" s="29" t="s">
         <v>269</v>
       </c>
-      <c r="F23" s="37" t="s">
+      <c r="F23" s="29" t="s">
         <v>208</v>
       </c>
       <c r="G23" s="7"/>
       <c r="H23" s="7"/>
     </row>
     <row r="24" spans="1:8" ht="79.95" customHeight="1">
-      <c r="A24" s="37" t="s">
+      <c r="A24" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="37" t="s">
+      <c r="B24" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="C24" s="37" t="s">
+      <c r="C24" s="29" t="s">
         <v>210</v>
       </c>
-      <c r="D24" s="37" t="s">
+      <c r="D24" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="E24" s="37" t="s">
+      <c r="E24" s="29" t="s">
         <v>270</v>
       </c>
-      <c r="F24" s="37" t="s">
+      <c r="F24" s="29" t="s">
         <v>212</v>
       </c>
       <c r="G24" s="7"/>
       <c r="H24" s="7"/>
     </row>
     <row r="25" spans="1:8" ht="79.95" customHeight="1">
-      <c r="A25" s="37" t="s">
+      <c r="A25" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="37" t="s">
+      <c r="B25" s="29" t="s">
         <v>213</v>
       </c>
-      <c r="C25" s="37" t="s">
+      <c r="C25" s="29" t="s">
         <v>214</v>
       </c>
-      <c r="D25" s="37" t="s">
+      <c r="D25" s="29" t="s">
         <v>215</v>
       </c>
-      <c r="E25" s="37" t="s">
+      <c r="E25" s="29" t="s">
         <v>271</v>
       </c>
-      <c r="F25" s="37" t="s">
+      <c r="F25" s="29" t="s">
         <v>216</v>
       </c>
       <c r="G25" s="7"/>
       <c r="H25" s="7"/>
     </row>
     <row r="26" spans="1:8" ht="79.95" customHeight="1">
-      <c r="A26" s="38" t="s">
+      <c r="A26" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="38" t="s">
+      <c r="B26" s="30" t="s">
         <v>217</v>
       </c>
-      <c r="C26" s="38" t="s">
+      <c r="C26" s="30" t="s">
         <v>218</v>
       </c>
-      <c r="D26" s="38" t="s">
+      <c r="D26" s="30" t="s">
         <v>219</v>
       </c>
-      <c r="E26" s="38" t="s">
+      <c r="E26" s="30" t="s">
         <v>220</v>
       </c>
-      <c r="F26" s="38" t="s">
+      <c r="F26" s="30" t="s">
         <v>221</v>
       </c>
       <c r="G26" s="7"/>
       <c r="H26" s="7"/>
     </row>
-    <row r="27" spans="1:8" ht="374.4">
-      <c r="A27" s="38" t="s">
+    <row r="27" spans="1:8" ht="331.2">
+      <c r="A27" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="B27" s="38" t="s">
+      <c r="B27" s="30" t="s">
         <v>222</v>
       </c>
-      <c r="C27" s="38" t="s">
+      <c r="C27" s="30" t="s">
         <v>223</v>
       </c>
-      <c r="D27" s="38" t="s">
+      <c r="D27" s="30" t="s">
         <v>224</v>
       </c>
-      <c r="E27" s="38" t="s">
+      <c r="E27" s="30" t="s">
         <v>225</v>
       </c>
-      <c r="F27" s="38" t="s">
+      <c r="F27" s="30" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="372.6">
-      <c r="A28" s="38" t="s">
+    <row r="28" spans="1:8" ht="345">
+      <c r="A28" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="39" t="s">
+      <c r="B28" s="31" t="s">
         <v>227</v>
       </c>
-      <c r="C28" s="39" t="s">
+      <c r="C28" s="31" t="s">
         <v>228</v>
       </c>
-      <c r="D28" s="39" t="s">
+      <c r="D28" s="31" t="s">
         <v>229</v>
       </c>
-      <c r="E28" s="39" t="s">
+      <c r="E28" s="31" t="s">
         <v>230</v>
       </c>
-      <c r="F28" s="40"/>
-    </row>
-    <row r="29" spans="1:8" ht="386.4">
-      <c r="A29" s="38" t="s">
+      <c r="F28" s="32"/>
+    </row>
+    <row r="29" spans="1:8" ht="317.39999999999998">
+      <c r="A29" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="38" t="s">
+      <c r="B29" s="30" t="s">
         <v>231</v>
       </c>
-      <c r="C29" s="41" t="s">
+      <c r="C29" s="33" t="s">
         <v>232</v>
       </c>
-      <c r="D29" s="41" t="s">
+      <c r="D29" s="33" t="s">
         <v>233</v>
       </c>
-      <c r="E29" s="41" t="s">
+      <c r="E29" s="33" t="s">
         <v>234</v>
       </c>
-      <c r="F29" s="42" t="s">
+      <c r="F29" s="34" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="372.6">
-      <c r="A30" s="43" t="s">
+    <row r="30" spans="1:8" ht="345">
+      <c r="A30" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="B30" s="39" t="s">
+      <c r="B30" s="31" t="s">
         <v>236</v>
       </c>
-      <c r="C30" s="39" t="s">
+      <c r="C30" s="31" t="s">
         <v>237</v>
       </c>
-      <c r="D30" s="39" t="s">
+      <c r="D30" s="31" t="s">
         <v>238</v>
       </c>
-      <c r="E30" s="39" t="s">
+      <c r="E30" s="31" t="s">
         <v>239</v>
       </c>
-      <c r="F30" s="40" t="s">
+      <c r="F30" s="32" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="386.4">
-      <c r="A31" s="43" t="s">
+    <row r="31" spans="1:8" ht="358.8">
+      <c r="A31" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="B31" s="39" t="s">
+      <c r="B31" s="31" t="s">
         <v>241</v>
       </c>
-      <c r="C31" s="39" t="s">
+      <c r="C31" s="31" t="s">
         <v>242</v>
       </c>
-      <c r="D31" s="39" t="s">
+      <c r="D31" s="31" t="s">
         <v>243</v>
       </c>
-      <c r="E31" s="39" t="s">
+      <c r="E31" s="31" t="s">
         <v>244</v>
       </c>
-      <c r="F31" s="40"/>
-    </row>
-    <row r="32" spans="1:8" ht="400.2">
-      <c r="A32" s="43" t="s">
+      <c r="F31" s="32"/>
+    </row>
+    <row r="32" spans="1:8" ht="358.8">
+      <c r="A32" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="B32" s="39" t="s">
+      <c r="B32" s="31" t="s">
         <v>245</v>
       </c>
-      <c r="C32" s="39" t="s">
+      <c r="C32" s="31" t="s">
         <v>246</v>
       </c>
-      <c r="D32" s="39" t="s">
+      <c r="D32" s="31" t="s">
         <v>247</v>
       </c>
-      <c r="E32" s="39" t="s">
+      <c r="E32" s="31" t="s">
         <v>248</v>
       </c>
-      <c r="F32" s="40"/>
-    </row>
-    <row r="33" spans="1:6" ht="409.6">
-      <c r="A33" s="43" t="s">
+      <c r="F32" s="32"/>
+    </row>
+    <row r="33" spans="1:6" ht="358.8">
+      <c r="A33" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="B33" s="39" t="s">
+      <c r="B33" s="31" t="s">
         <v>249</v>
       </c>
-      <c r="C33" s="39" t="s">
+      <c r="C33" s="31" t="s">
         <v>250</v>
       </c>
-      <c r="D33" s="39" t="s">
+      <c r="D33" s="31" t="s">
         <v>251</v>
       </c>
-      <c r="E33" s="39" t="s">
+      <c r="E33" s="31" t="s">
         <v>252</v>
       </c>
-      <c r="F33" s="40" t="s">
+      <c r="F33" s="32" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="372.6">
-      <c r="A34" s="43" t="s">
+    <row r="34" spans="1:6" ht="345">
+      <c r="A34" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="B34" s="39" t="s">
+      <c r="B34" s="31" t="s">
         <v>254</v>
       </c>
-      <c r="C34" s="39" t="s">
+      <c r="C34" s="31" t="s">
         <v>255</v>
       </c>
-      <c r="D34" s="39" t="s">
+      <c r="D34" s="31" t="s">
         <v>256</v>
       </c>
-      <c r="E34" s="39" t="s">
+      <c r="E34" s="31" t="s">
         <v>257</v>
       </c>
-      <c r="F34" s="40"/>
-    </row>
-    <row r="35" spans="1:6" ht="409.6">
-      <c r="A35" s="43" t="s">
+      <c r="F34" s="32"/>
+    </row>
+    <row r="35" spans="1:6" ht="400.2">
+      <c r="A35" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="B35" s="39" t="s">
+      <c r="B35" s="31" t="s">
         <v>258</v>
       </c>
-      <c r="C35" s="39" t="s">
+      <c r="C35" s="31" t="s">
         <v>259</v>
       </c>
-      <c r="D35" s="39" t="s">
+      <c r="D35" s="31" t="s">
         <v>260</v>
       </c>
-      <c r="E35" s="39" t="s">
+      <c r="E35" s="31" t="s">
         <v>261</v>
       </c>
-      <c r="F35" s="40"/>
+      <c r="F35" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3533,24 +3527,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="46" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="45" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
     </row>
     <row r="3" spans="1:6" ht="40.049999999999997" customHeight="1">
       <c r="A3" s="6" t="s">
@@ -3573,7 +3567,7 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="60" customHeight="1">
-      <c r="A4" s="47">
+      <c r="A4" s="38">
         <v>5</v>
       </c>
       <c r="B4" s="7" t="s">
@@ -3593,82 +3587,82 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="100.8">
-      <c r="A5" s="36">
+      <c r="A5" s="28">
         <v>3</v>
       </c>
-      <c r="B5" s="36" t="s">
+      <c r="B5" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="C5" s="36" t="s">
+      <c r="C5" s="28" t="s">
         <v>273</v>
       </c>
-      <c r="D5" s="36" t="s">
+      <c r="D5" s="28" t="s">
         <v>274</v>
       </c>
-      <c r="E5" s="36" t="s">
+      <c r="E5" s="28" t="s">
         <v>275</v>
       </c>
-      <c r="F5" s="36" t="s">
+      <c r="F5" s="28" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="60" customHeight="1">
-      <c r="A6" s="36">
+      <c r="A6" s="28">
         <v>9</v>
       </c>
-      <c r="B6" s="36" t="s">
+      <c r="B6" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="C6" s="36" t="s">
+      <c r="C6" s="28" t="s">
         <v>277</v>
       </c>
-      <c r="D6" s="36" t="s">
+      <c r="D6" s="28" t="s">
         <v>278</v>
       </c>
-      <c r="E6" s="36" t="s">
+      <c r="E6" s="28" t="s">
         <v>279</v>
       </c>
-      <c r="F6" s="36" t="s">
+      <c r="F6" s="28" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="60" customHeight="1">
-      <c r="A7" s="48">
+      <c r="A7" s="39">
         <v>13</v>
       </c>
-      <c r="B7" s="49" t="s">
+      <c r="B7" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="C7" s="49" t="s">
+      <c r="C7" s="40" t="s">
         <v>281</v>
       </c>
-      <c r="D7" s="49" t="s">
+      <c r="D7" s="40" t="s">
         <v>282</v>
       </c>
-      <c r="E7" s="49" t="s">
+      <c r="E7" s="40" t="s">
         <v>283</v>
       </c>
-      <c r="F7" s="49" t="s">
+      <c r="F7" s="40" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="60" customHeight="1">
-      <c r="A8" s="48">
+      <c r="A8" s="39">
         <v>17</v>
       </c>
-      <c r="B8" s="49" t="s">
+      <c r="B8" s="40" t="s">
         <v>69</v>
       </c>
-      <c r="C8" s="49" t="s">
+      <c r="C8" s="40" t="s">
         <v>285</v>
       </c>
-      <c r="D8" s="49" t="s">
+      <c r="D8" s="40" t="s">
         <v>286</v>
       </c>
-      <c r="E8" s="49" t="s">
+      <c r="E8" s="40" t="s">
         <v>287</v>
       </c>
-      <c r="F8" s="49" t="s">
+      <c r="F8" s="40" t="s">
         <v>288</v>
       </c>
     </row>
@@ -3892,20 +3886,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="42" t="s">
         <v>72</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="47" t="s">
         <v>73</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
     </row>
     <row r="4" spans="1:4" ht="18">
       <c r="A4" s="1" t="s">
@@ -3933,10 +3927,10 @@
       <c r="B6" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="25" t="s">
         <v>158</v>
       </c>
-      <c r="D6" s="29" t="s">
+      <c r="D6" s="27" t="s">
         <v>168</v>
       </c>
     </row>
@@ -3947,10 +3941,10 @@
       <c r="B7" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="25" t="s">
         <v>158</v>
       </c>
-      <c r="D7" s="29" t="s">
+      <c r="D7" s="27" t="s">
         <v>169</v>
       </c>
     </row>
@@ -3961,10 +3955,10 @@
       <c r="B8" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="25" t="s">
         <v>158</v>
       </c>
-      <c r="D8" s="29" t="s">
+      <c r="D8" s="27" t="s">
         <v>170</v>
       </c>
     </row>
@@ -3975,10 +3969,10 @@
       <c r="B9" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="C9" s="26" t="s">
+      <c r="C9" s="25" t="s">
         <v>158</v>
       </c>
-      <c r="D9" s="29" t="s">
+      <c r="D9" s="27" t="s">
         <v>171</v>
       </c>
     </row>
@@ -3989,10 +3983,10 @@
       <c r="B10" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="25" t="s">
         <v>158</v>
       </c>
-      <c r="D10" s="29" t="s">
+      <c r="D10" s="27" t="s">
         <v>172</v>
       </c>
     </row>
@@ -4022,10 +4016,10 @@
       <c r="B14" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="C14" s="26" t="s">
+      <c r="C14" s="25" t="s">
         <v>158</v>
       </c>
-      <c r="D14" s="29" t="s">
+      <c r="D14" s="27" t="s">
         <v>173</v>
       </c>
     </row>
@@ -4036,7 +4030,7 @@
       <c r="B15" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="C15" s="26" t="s">
+      <c r="C15" s="25" t="s">
         <v>158</v>
       </c>
       <c r="D15" s="18" t="s">
@@ -4050,10 +4044,10 @@
       <c r="B16" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="C16" s="26" t="s">
+      <c r="C16" s="25" t="s">
         <v>158</v>
       </c>
-      <c r="D16" s="29" t="s">
+      <c r="D16" s="27" t="s">
         <v>174</v>
       </c>
     </row>
@@ -4064,10 +4058,10 @@
       <c r="B17" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="C17" s="26" t="s">
+      <c r="C17" s="25" t="s">
         <v>158</v>
       </c>
-      <c r="D17" s="29" t="s">
+      <c r="D17" s="27" t="s">
         <v>175</v>
       </c>
     </row>
@@ -4078,10 +4072,10 @@
       <c r="B18" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="C18" s="26" t="s">
+      <c r="C18" s="25" t="s">
         <v>158</v>
       </c>
-      <c r="D18" s="25" t="s">
+      <c r="D18" s="24" t="s">
         <v>156</v>
       </c>
     </row>
@@ -4170,72 +4164,72 @@
     <row r="33" spans="1:4" ht="67.8" customHeight="1"/>
     <row r="34" spans="1:4" ht="99.6" customHeight="1"/>
     <row r="35" spans="1:4" ht="72">
-      <c r="A35" s="37">
+      <c r="A35" s="29">
         <v>4</v>
       </c>
-      <c r="B35" s="37" t="s">
+      <c r="B35" s="29" t="s">
         <v>289</v>
       </c>
-      <c r="C35" s="37" t="s">
+      <c r="C35" s="29" t="s">
         <v>290</v>
       </c>
-      <c r="D35" s="37" t="s">
+      <c r="D35" s="29" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="86.4">
-      <c r="A36" s="37">
+      <c r="A36" s="29">
         <v>5</v>
       </c>
-      <c r="B36" s="37" t="s">
+      <c r="B36" s="29" t="s">
         <v>292</v>
       </c>
-      <c r="C36" s="37" t="s">
+      <c r="C36" s="29" t="s">
         <v>293</v>
       </c>
-      <c r="D36" s="37" t="s">
+      <c r="D36" s="29" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="72">
-      <c r="A37" s="37">
+      <c r="A37" s="29">
         <v>6</v>
       </c>
-      <c r="B37" s="37" t="s">
+      <c r="B37" s="29" t="s">
         <v>295</v>
       </c>
-      <c r="C37" s="37" t="s">
+      <c r="C37" s="29" t="s">
         <v>296</v>
       </c>
-      <c r="D37" s="37" t="s">
+      <c r="D37" s="29" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="86.4">
-      <c r="A38" s="50">
+      <c r="A38" s="41">
         <v>7</v>
       </c>
-      <c r="B38" s="50" t="s">
+      <c r="B38" s="41" t="s">
         <v>298</v>
       </c>
-      <c r="C38" s="50" t="s">
+      <c r="C38" s="41" t="s">
         <v>299</v>
       </c>
-      <c r="D38" s="50" t="s">
+      <c r="D38" s="41" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="72">
-      <c r="A39" s="50">
+      <c r="A39" s="41">
         <v>8</v>
       </c>
-      <c r="B39" s="50" t="s">
+      <c r="B39" s="41" t="s">
         <v>301</v>
       </c>
-      <c r="C39" s="50" t="s">
+      <c r="C39" s="41" t="s">
         <v>302</v>
       </c>
-      <c r="D39" s="50" t="s">
+      <c r="D39" s="41" t="s">
         <v>297</v>
       </c>
     </row>
